--- a/templates/pustaka-template.xlsx
+++ b/templates/pustaka-template.xlsx
@@ -113,7 +113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,18 +123,34 @@
     <font>
       <family val="2"/>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B4F72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EAF8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -142,14 +158,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFC9CA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFC9CA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFC9CA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFC9CA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -421,10 +457,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="4" min="1" width="18"/>
+    <col customWidth="true" max="1" min="1" width="32"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
+    <col customWidth="true" max="3" min="3" width="45"/>
+    <col customWidth="true" max="4" min="4" width="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,117 +478,302 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" sqref="D2:D39" type="list">
+      <formula1>"harga,statistik,berita,regulasi,umum"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
--- a/templates/pustaka-template.xlsx
+++ b/templates/pustaka-template.xlsx
@@ -8,112 +8,199 @@
   </bookViews>
   <sheets>
     <sheet name="Pustaka" sheetId="1" r:id="rId1"/>
+    <sheet name="Petunjuk" sheetId="2" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Pustaka'!$A$1:$D$39</definedName>
+  </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Kios Cerdas</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <t>⚠️ WAJIB DIISI
+Judul sumber referensi.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>ℹ️ Opsional
+Deskripsi singkat tentang sumber ini.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <t>ℹ️ Opsional
+URL/tautan ke sumber referensi.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <t>ℹ️ Opsional
+Kategori sumber. Pilih dari dropdown.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+  <si>
+    <t>judul *</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>kategori</t>
+  </si>
+  <si>
+    <t>Panel Harga Badan Pangan</t>
+  </si>
+  <si>
+    <t>Harga pangan harian nasional (beras gula minyak dll)</t>
+  </si>
+  <si>
+    <t>https://panelharga.badanpangan.go.id</t>
+  </si>
+  <si>
+    <t>harga</t>
+  </si>
+  <si>
+    <t>PIHPS Bank Indonesia</t>
+  </si>
+  <si>
+    <t>Harga pangan strategis antarwilayah</t>
+  </si>
+  <si>
+    <t>https://www.bi.go.id/hargapangan</t>
+  </si>
+  <si>
+    <t>Kemendag SP2KP/EWS</t>
+  </si>
+  <si>
+    <t>Harga &amp; pasokan bahan pokok nasional</t>
+  </si>
+  <si>
+    <t>https://ews.kemendag.go.id</t>
+  </si>
+  <si>
+    <t>Distan &amp; Ketahanan Pangan NTT</t>
+  </si>
+  <si>
+    <t>Harga komoditi pasar Kupang (update mingguan)</t>
+  </si>
+  <si>
+    <t>https://distankp.nttprov.go.id</t>
+  </si>
+  <si>
+    <t>BPS Nusa Tenggara Timur</t>
+  </si>
+  <si>
+    <t>Inflasi &amp; statistik harga NTT</t>
+  </si>
+  <si>
+    <t>https://ntt.bps.go.id</t>
+  </si>
+  <si>
+    <t>statistik</t>
+  </si>
+  <si>
+    <t>ANTARA Kupang</t>
+  </si>
+  <si>
+    <t>Berita ekonomi &amp; harga pangan NTT</t>
+  </si>
+  <si>
+    <t>https://kupang.antaranews.com</t>
+  </si>
+  <si>
+    <t>berita</t>
+  </si>
+  <si>
+    <t>Pemkab Rote Ndao</t>
+  </si>
+  <si>
+    <t>Berita &amp; program pangan daerah</t>
+  </si>
+  <si>
+    <t>https://rotendaokab.go.id</t>
+  </si>
+  <si>
+    <t>OnlineNTT</t>
+  </si>
+  <si>
+    <t>Berita lokal Rote Ndao &amp; NTT</t>
+  </si>
+  <si>
+    <t>https://www.onlinentt.com</t>
+  </si>
+  <si>
+    <t>Panduan Pengisian Template</t>
+  </si>
+  <si>
+    <t>Template ini untuk mengimport data pustaka ke Kios Cerdas.
+Isi kolom sesuai panduan, lalu simpan dan import via bot Telegram.</t>
+  </si>
+  <si>
+    <t>Kolom</t>
+  </si>
+  <si>
+    <t>Wajib?</t>
+  </si>
+  <si>
+    <t>Contoh</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>Validasi</t>
+  </si>
   <si>
     <t>judul</t>
   </si>
   <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>kategori</t>
-  </si>
-  <si>
-    <t>Panel Harga Badan Pangan</t>
-  </si>
-  <si>
-    <t>Harga pangan harian nasional</t>
-  </si>
-  <si>
-    <t>https://panelharga.badanpangan.go.id</t>
-  </si>
-  <si>
-    <t>harga</t>
-  </si>
-  <si>
-    <t>PIHPS Bank Indonesia</t>
-  </si>
-  <si>
-    <t>Harga pangan strategis antarwilayah</t>
-  </si>
-  <si>
-    <t>https://www.bi.go.id/hargapangan</t>
-  </si>
-  <si>
-    <t>Kemendag SP2KP/EWS</t>
-  </si>
-  <si>
-    <t>Harga &amp; pasokan bahan pokok nasional</t>
-  </si>
-  <si>
-    <t>https://ews.kemendag.go.id</t>
-  </si>
-  <si>
-    <t>Distan &amp; Ketahanan Pangan NTT</t>
-  </si>
-  <si>
-    <t>Harga komoditi pasar Kupang (mingguan)</t>
-  </si>
-  <si>
-    <t>https://distankp.nttprov.go.id</t>
-  </si>
-  <si>
-    <t>BPS Nusa Tenggara Timur</t>
-  </si>
-  <si>
-    <t>Inflasi &amp; statistik harga NTT</t>
-  </si>
-  <si>
-    <t>https://ntt.bps.go.id</t>
-  </si>
-  <si>
-    <t>statistik</t>
-  </si>
-  <si>
-    <t>ANTARA Kupang</t>
-  </si>
-  <si>
-    <t>Berita ekonomi &amp; harga pangan NTT</t>
-  </si>
-  <si>
-    <t>https://kupang.antaranews.com</t>
-  </si>
-  <si>
-    <t>berita</t>
-  </si>
-  <si>
-    <t>Pemkab Rote Ndao</t>
-  </si>
-  <si>
-    <t>Berita &amp; program pangan daerah</t>
-  </si>
-  <si>
-    <t>https://rotendaokab.go.id</t>
-  </si>
-  <si>
-    <t>OnlineNTT</t>
-  </si>
-  <si>
-    <t>Berita lokal Rote Ndao &amp; NTT</t>
-  </si>
-  <si>
-    <t>https://www.onlinentt.com</t>
+    <t>WAJIB</t>
+  </si>
+  <si>
+    <t>Judul sumber referensi.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Opsional</t>
+  </si>
+  <si>
+    <t>Deskripsi singkat tentang sumber ini.</t>
+  </si>
+  <si>
+    <t>URL/tautan ke sumber referensi.</t>
+  </si>
+  <si>
+    <t>Kategori sumber. Pilih dari dropdown.</t>
+  </si>
+  <si>
+    <t>Pilih dari dropdown</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,11 +211,34 @@
       <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF2D3436"/>
       <sz val="11"/>
     </font>
     <font>
       <family val="2"/>
-      <color/>
+      <b val="1"/>
+      <color rgb="FF0D7C66"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF555555"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFC0392B"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -141,12 +251,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B4F72"/>
+        <fgColor rgb="FF0D7C66"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6EAF8"/>
+        <fgColor rgb="FFF0F7F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -160,23 +270,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFC9CA"/>
+        <color rgb="FFCCDDC8"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFC9CA"/>
+        <color rgb="FFCCDDC8"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFC9CA"/>
+        <color rgb="FFCCDDC8"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFC9CA"/>
+        <color rgb="FFCCDDC8"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -186,6 +296,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,6 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -463,7 +589,7 @@
     <col customWidth="true" max="4" min="4" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="true">
+    <row r="1" ht="32" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -770,10 +896,126 @@
       <c r="D39" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="$A$1:$D$39"/>
   <dataValidations count="1">
     <dataValidation allowBlank="true" sqref="D2:D39" type="list">
       <formula1>"harga,statistik,berita,regulasi,umum"</formula1>
     </dataValidation>
   </dataValidations>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="22"/>
+    <col customWidth="true" max="2" min="2" width="12"/>
+    <col customWidth="true" max="3" min="3" width="40"/>
+    <col customWidth="true" max="4" min="4" width="46"/>
+    <col customWidth="true" max="5" min="5" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="true">
+      <c r="A1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="true">
+      <c r="A2" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="true">
+      <c r="A5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="true">
+      <c r="A6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="true">
+      <c r="A7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="true">
+      <c r="A8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
 </worksheet>
 </file>